--- a/slab_detailer/improtntinos4_output/improtntinos4_bar_schedule.xlsx
+++ b/slab_detailer/improtntinos4_output/improtntinos4_bar_schedule.xlsx
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>4820</v>
+        <v>4810</v>
       </c>
       <c r="H43" t="n">
         <v>3</v>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>3Φ12x482/20</t>
+          <t>3Φ12x481/20</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5810</v>
+        <v>5820</v>
       </c>
       <c r="H62" t="n">
         <v>3</v>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>3Φ12x581/20</t>
+          <t>3Φ12x582/20</t>
         </is>
       </c>
     </row>
